--- a/stories/arbres/ATOM-SEC.PAR.001-02.xlsx
+++ b/stories/arbres/ATOM-SEC.PAR.001-02.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Zoé arrive au jardin public. Papa montre un espace. C'est près des cerceaux colorés. Papa dit : tu joues ici, dans l'espace montré. Ici, l'adulte voit. Zoé prend un cerceau. Elle le fait rouler. Papa s'assoit sur le banc. Parce que Zoé reste dans l'espace montré, papa la voit. Zoé fait un grand cercle. Elle revient près du banc. Papa dit : je te vois. L'adulte voit. Zoé pose le cerceau. Elle reste dans l'espace montré. Le vent est doux. Zoé rit. Papa tape dans ses mains.</t>
+          <t>Zoé arrive au jardin public. Papa montre un espace. C'est près des cerceaux colorés. Tu joues ici, dans l'espace montré. Ici, l'adulte voit. Zoé prend un cerceau. Elle le fait rouler. Papa s'assoit sur le banc. Parce que Zoé reste dans l'espace montré, papa la voit. Zoé fait un grand cercle. Elle revient près du banc. Je te vois. L'adulte voit. Zoé pose le cerceau. Elle reste dans l'espace montré. Le vent est doux. Zoé rit. Papa tape dans ses mains.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,15 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Zoé arrive au jardin public. Papa montre un espace. C'est près des cerceaux colorés.
+papa|Tu joues ici, dans l'espace montré. Ici, l'adulte voit.
+narrateur|Zoé prend un cerceau. Elle le fait rouler. Papa s'assoit sur le banc. Parce que Zoé reste dans l'espace montré, papa la voit. Zoé fait un grand cercle. Elle revient près du banc.
+papa|Je te vois. L'adulte voit.
+narrateur|Zoé pose le cerceau. Elle reste dans l'espace montré. Le vent est doux. Zoé rit. Papa tape dans ses mains.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1465,6 +1490,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Zoé joue au jardin. Où reste-t-elle ?</t>
         </is>
       </c>
     </row>
@@ -1633,6 +1663,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Zoé est restée dans l'espace montré. Parce qu'elle y est restée, papa la voyait.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1791,6 +1826,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Zoé range le cerceau. Papa lui tend la gourde.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1953,6 +1993,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1971,7 +2016,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1988,6 +2033,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SEC.PAR.001-02.xlsx
+++ b/stories/arbres/ATOM-SEC.PAR.001-02.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1314,6 +1319,11 @@
 narrateur|Zoé pose le cerceau. Elle reste dans l'espace montré. Le vent est doux. Zoé rit. Papa tape dans ses mains.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1497,6 +1507,7 @@
           <t>narrateur|Zoé joue au jardin. Où reste-t-elle ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1668,6 +1679,11 @@
           <t>narrateur|Zoé est restée dans l'espace montré. Parce qu'elle y est restée, papa la voyait.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1831,6 +1847,7 @@
           <t>narrateur|Zoé range le cerceau. Papa lui tend la gourde.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1998,6 +2015,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2016,7 +2034,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2040,6 +2058,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2054,7 +2086,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2241,6 +2273,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-SEC.PAR.001-02.xlsx
+++ b/stories/arbres/ATOM-SEC.PAR.001-02.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Zoé et les cerceaux</t>
+          <t>Le cerceau orange de Mila</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Une petite bête rouge marche sur le cerceau de Mila. Papa montre l'espace près des cerceaux. Mila reste où l'adulte voit.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1184,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Zoé arrive au jardin public. Papa montre un espace. C'est près des cerceaux colorés. Tu joues ici, dans l'espace montré. Ici, l'adulte voit. Zoé prend un cerceau. Elle le fait rouler. Papa s'assoit sur le banc. Parce que Zoé reste dans l'espace montré, papa la voit. Zoé fait un grand cercle. Elle revient près du banc. Je te vois. L'adulte voit. Zoé pose le cerceau. Elle reste dans l'espace montré. Le vent est doux. Zoé rit. Papa tape dans ses mains.</t>
+          <t>Une petite bête rouge marche sur un cerceau. Le cerceau est orange et un peu froid. Le tilleul fait une ombre ronde. Une feuille tombe, toute lente. Le banc sent le bois chaud. Une fourmi croise la feuille. Tu as vu la petite bête, Mila ? Elle est rouge, papa. Oui. Elle a des points noirs. Mila se penche tout doux. La petite bête lève une patte. Elle marche. Tout doucement, oui. La petite bête va sous une feuille. En ce moment, papa montre un espace. C'est près des cerceaux colorés. Tu joues ici. Dans l'espace montré. Ici, l'adulte voit. Mila prend un cerceau orange. Le plastique est un peu froid. Elle le fait rouler. Le cerceau fait un petit rum. Papa s'assoit sur le banc. Parce que Mila reste dans l'espace montré, papa la voit. L'adulte voit. Il roule, papa. Oui. Tu restes près des cerceaux. Je te vois. Mila fait un grand cercle. L'ombre du tilleul tourne avec elle. Elle revient près du banc. Tu es dans l'espace montré ? Oui. Bravo. Le vent est doux. L'ombre du tilleul bouge un peu. On recommence un tour ? Oui, papa. Mila fait rouler encore le cerceau. Le rum revient, tout rond. Elle reste dans l'espace montré. L'adulte voit. Tu as fait du bon travail. La petite bête est partie. Oui. Toi, tu es restée ici. Mila pose le cerceau. Mila tape dans ses mains. Papa tape aussi. Le cerceau orange brille au soleil.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,11 +1324,59 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Zoé arrive au jardin public. Papa montre un espace. C'est près des cerceaux colorés.
-papa|Tu joues ici, dans l'espace montré. Ici, l'adulte voit.
-narrateur|Zoé prend un cerceau. Elle le fait rouler. Papa s'assoit sur le banc. Parce que Zoé reste dans l'espace montré, papa la voit. Zoé fait un grand cercle. Elle revient près du banc.
-papa|Je te vois. L'adulte voit.
-narrateur|Zoé pose le cerceau. Elle reste dans l'espace montré. Le vent est doux. Zoé rit. Papa tape dans ses mains.</t>
+          <t>narrateur|Une petite bête rouge marche sur un cerceau.
+narrateur|Le cerceau est orange et un peu froid.
+narrateur|Le tilleul fait une ombre ronde.
+narrateur|Une feuille tombe, toute lente.
+narrateur|Le banc sent le bois chaud.
+narrateur|Une fourmi croise la feuille.
+papa|Tu as vu la petite bête, Mila ?
+enfant-f|Elle est rouge, papa.
+papa|Oui.
+papa|Elle a des points noirs.
+narrateur|Mila se penche tout doux.
+narrateur|La petite bête lève une patte.
+enfant-f|Elle marche.
+papa|Tout doucement, oui.
+narrateur|La petite bête va sous une feuille.
+narrateur|En ce moment, papa montre un espace.
+narrateur|C'est près des cerceaux colorés.
+papa|Tu joues ici.
+papa|Dans l'espace montré.
+papa|Ici, l'adulte voit.
+narrateur|Mila prend un cerceau orange.
+narrateur|Le plastique est un peu froid.
+narrateur|Elle le fait rouler.
+narrateur|Le cerceau fait un petit rum.
+narrateur|Papa s'assoit sur le banc.
+narrateur|Parce que Mila reste dans l'espace montré, papa la voit.
+narrateur|L'adulte voit.
+enfant-f|Il roule, papa.
+papa|Oui.
+papa|Tu restes près des cerceaux.
+papa|Je te vois.
+narrateur|Mila fait un grand cercle.
+narrateur|L'ombre du tilleul tourne avec elle.
+narrateur|Elle revient près du banc.
+papa|Tu es dans l'espace montré ?
+enfant-f|Oui.
+papa|Bravo.
+narrateur|Le vent est doux.
+narrateur|L'ombre du tilleul bouge un peu.
+papa|On recommence un tour ?
+enfant-f|Oui, papa.
+narrateur|Mila fait rouler encore le cerceau.
+narrateur|Le rum revient, tout rond.
+narrateur|Elle reste dans l'espace montré.
+papa|L'adulte voit.
+papa|Tu as fait du bon travail.
+enfant-f|La petite bête est partie.
+papa|Oui.
+papa|Toi, tu es restée ici.
+narrateur|Mila pose le cerceau.
+narrateur|Mila tape dans ses mains.
+narrateur|Papa tape aussi.
+narrateur|Le cerceau orange brille au soleil.</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
@@ -1348,7 +1408,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Zoé joue au jardin. Où reste-t-elle ?</t>
+          <t>Mila joue au jardin. Où reste-t-elle ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1504,10 +1564,10 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Zoé joue au jardin. Où reste-t-elle ?</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr"/>
+          <t>narrateur|Mila joue au jardin.
+narrateur|Où reste-t-elle ?</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1532,7 +1592,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Zoé est restée dans l'espace montré. Parce qu'elle y est restée, papa la voyait.</t>
+          <t>Mila est restée dans l'espace montré. Parce qu'elle y est restée, papa la voyait. L'adulte voit. Tu es restée dans l'espace montré ? Oui, papa. Bravo. Je te voyais. Le cerceau orange est posé. L'ombre du tilleul est ronde.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1676,7 +1736,15 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Zoé est restée dans l'espace montré. Parce qu'elle y est restée, papa la voyait.</t>
+          <t>narrateur|Mila est restée dans l'espace montré.
+narrateur|Parce qu'elle y est restée, papa la voyait.
+narrateur|L'adulte voit.
+papa|Tu es restée dans l'espace montré ?
+enfant-f|Oui, papa.
+papa|Bravo.
+papa|Je te voyais.
+narrateur|Le cerceau orange est posé.
+narrateur|L'ombre du tilleul est ronde.</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
@@ -1708,7 +1776,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Zoé range le cerceau. Papa lui tend la gourde.</t>
+          <t>Mila range le cerceau. Le plastique n'est plus froid. Papa lui tend la gourde. L'eau est fraîche. Tu as soif ? Un peu. Bois. Tu as joué dans l'espace montré. Oui. L'adulte voit. Bravo, Mila. Mila boit. Une goutte tombe sur sa main. Le tilleul sent fort, tout près.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1844,10 +1912,22 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Zoé range le cerceau. Papa lui tend la gourde.</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr"/>
+          <t>narrateur|Mila range le cerceau.
+narrateur|Le plastique n'est plus froid.
+narrateur|Papa lui tend la gourde.
+narrateur|L'eau est fraîche.
+papa|Tu as soif ?
+enfant-f|Un peu.
+papa|Bois.
+papa|Tu as joué dans l'espace montré.
+enfant-f|Oui.
+papa|L'adulte voit.
+papa|Bravo, Mila.
+narrateur|Mila boit.
+narrateur|Une goutte tombe sur sa main.
+narrateur|Le tilleul sent fort, tout près.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1872,7 +1952,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Le cerceau orange rentre dans le sac. J'ai fait rouler le cerceau. Oui. Dans l'espace montré. Bravo, Mila. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2012,10 +2092,14 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+          <t>narrateur|Le cerceau orange rentre dans le sac.
+enfant-f|J'ai fait rouler le cerceau.
+papa|Oui.
+papa|Dans l'espace montré.
+papa|Bravo, Mila.
+narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2034,7 +2118,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2072,6 +2156,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SEC.PAR.001-02.xlsx
+++ b/stories/arbres/ATOM-SEC.PAR.001-02.xlsx
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Une petite bête rouge marche sur un cerceau. Le cerceau est orange et un peu froid. Le tilleul fait une ombre ronde. Une feuille tombe, toute lente. Le banc sent le bois chaud. Une fourmi croise la feuille. Tu as vu la petite bête, Mila ? Elle est rouge, papa. Oui. Elle a des points noirs. Mila se penche tout doux. La petite bête lève une patte. Elle marche. Tout doucement, oui. La petite bête va sous une feuille. En ce moment, papa montre un espace. C'est près des cerceaux colorés. Tu joues ici. Dans l'espace montré. Ici, l'adulte voit. Mila prend un cerceau orange. Le plastique est un peu froid. Elle le fait rouler. Le cerceau fait un petit rum. Papa s'assoit sur le banc. Parce que Mila reste dans l'espace montré, papa la voit. L'adulte voit. Il roule, papa. Oui. Tu restes près des cerceaux. Je te vois. Mila fait un grand cercle. L'ombre du tilleul tourne avec elle. Elle revient près du banc. Tu es dans l'espace montré ? Oui. Bravo. Le vent est doux. L'ombre du tilleul bouge un peu. On recommence un tour ? Oui, papa. Mila fait rouler encore le cerceau. Le rum revient, tout rond. Elle reste dans l'espace montré. L'adulte voit. Tu as fait du bon travail. La petite bête est partie. Oui. Toi, tu es restée ici. Mila pose le cerceau. Mila tape dans ses mains. Papa tape aussi. Le cerceau orange brille au soleil.</t>
+          <t>Une petite bête rouge marche sur un cerceau. Le cerceau est orange et un peu froid. Le tilleul fait une ombre ronde. Une feuille tombe, toute lente. Le banc sent le bois chaud. Une fourmi croise la feuille. Tu as vu la petite bête, Mila ? Elle est rouge, papa. Oui. Elle a des points noirs. Mila se penche tout doux. La petite bête lève une patte. Elle marche. Tout doucement, oui. La petite bête va sous une feuille. En ce moment, papa montre un espace. C'est près des cerceaux colorés. Tu joues ici. Dans l'espace montré. Ici, l'adulte voit. Mila prend un cerceau orange. Le plastique est un peu froid. Elle le fait rouler. Le cerceau fait un petit rum. Papa s'assoit sur le banc. Parce que Mila reste dans l'espace montré, papa la voit. L'adulte voit. Il roule, papa. Oui. Tu restes près des cerceaux. Je te vois. Mila fait un grand cercle. L'ombre du tilleul tourne avec elle. Elle revient près du banc. Tu es dans l'espace montré ? Oui. Bravo. Le vent est doux. L'ombre du tilleul bouge un peu. On recommence un tour ? Oui, papa. Mila fait rouler encore le cerceau. Le rum revient, tout rond. Elle reste dans l'espace montré. L'adulte voit. La petite bête est partie. Oui. Toi, tu es restée ici. Mila pose le cerceau. Mila tape dans ses mains. Papa tape aussi. Le cerceau orange brille au soleil.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Zoé arrive au jardin public. Papa montre un &lt;emphasis level="moderate"&gt;espace&lt;/emphasis&gt;. C'est près des cerceaux colorés. Papa dit : tu joues ici, dans l'espace montré. Ici, l'adulte voit. Zoé prend un cerceau. Elle le fait rouler. Papa s'assoit sur le banc. Parce que Zoé reste dans l'espace montré, papa la voit. Zoé fait un grand cercle. Elle revient près du banc. Papa dit : je te vois. L'adulte voit. Zoé pose le cerceau. Elle reste dans l'espace montré. Le vent est doux. Zoé rit. Papa tape dans ses mains.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>Une petite bête rouge marche sur un cerceau. Le cerceau est orange et un peu froid. Le tilleul fait une ombre ronde. Une feuille tombe, toute lente. Le banc sent le bois chaud. Une fourmi croise la feuille. Tu as vu la petite bête, Mila ? Elle est rouge, papa. Oui. Elle a des points noirs. Mila se penche tout doux. La petite bête lève une patte. Elle marche. Tout doucement, oui. La petite bête va sous une feuille. En ce moment, papa montre un espace. C'est près des cerceaux colorés. Tu joues ici. Dans l'espace montré. Ici, l'adulte voit. Mila prend un cerceau orange. Le plastique est un peu froid. Elle le fait rouler. Le cerceau fait un petit rum. Papa s'assoit sur le banc. Parce que Mila reste dans l'espace montré, papa la voit. L'adulte voit. Il roule, papa. Oui. Tu restes près des cerceaux. Je te vois. Mila fait un grand cercle. L'ombre du tilleul tourne avec elle. Elle revient près du banc. Tu es dans l'espace montré ? Oui. Bravo. Le vent est doux. L'ombre du tilleul bouge un peu. On recommence un tour ? Oui, papa. Mila fait rouler encore le cerceau. Le rum revient, tout rond. Elle reste dans l'espace montré. L'adulte voit. La petite bête est partie. Oui. Toi, tu es restée ici. Mila pose le cerceau. Mila tape dans ses mains. Papa tape aussi. Le cerceau orange brille au soleil.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1369,7 +1369,6 @@
 narrateur|Le rum revient, tout rond.
 narrateur|Elle reste dans l'espace montré.
 papa|L'adulte voit.
-papa|Tu as fait du bon travail.
 enfant-f|La petite bête est partie.
 papa|Oui.
 papa|Toi, tu es restée ici.
@@ -1413,7 +1412,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Zoé joue au jardin. Où reste-t-elle ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Mila joue au jardin. Où reste-t-elle ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1597,7 +1596,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Zoé est restée dans l'&lt;emphasis level="moderate"&gt;espace&lt;/emphasis&gt; montré. Parce qu'elle y est restée, papa la voyait.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Mila est restée dans l'espace montré. Parce qu'elle y est restée, papa la voyait. L'adulte voit. Tu es restée dans l'espace montré ? Oui, papa. Bravo. Je te voyais. Le cerceau orange est posé. L'ombre du tilleul est ronde.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1781,7 +1780,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Zoé range le cerceau. Papa lui tend la gourde.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Mila range le cerceau. Le plastique n'est plus froid. Papa lui tend la gourde. L'eau est fraîche. Tu as soif ? Un peu. Bois. Tu as joué dans l'espace montré. Oui. L'adulte voit. Bravo, Mila. Mila boit. Une goutte tombe sur sa main. Le tilleul sent fort, tout près.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1952,12 +1951,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Le cerceau orange rentre dans le sac. J'ai fait rouler le cerceau. Oui. Dans l'espace montré. Bravo, Mila. L'histoire est finie.</t>
+          <t>Le cerceau orange rentre dans le sac. J'ai fait rouler le cerceau. Oui. Dans l'espace montré. Bravo, Mila.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>Le cerceau orange rentre dans le sac. J'ai fait rouler le cerceau. Oui. Dans l'espace montré. Bravo, Mila.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2096,8 +2095,7 @@
 enfant-f|J'ai fait rouler le cerceau.
 papa|Oui.
 papa|Dans l'espace montré.
-papa|Bravo, Mila.
-narrateur|L'histoire est finie.</t>
+papa|Bravo, Mila.</t>
         </is>
       </c>
     </row>
@@ -2118,7 +2116,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2163,6 +2161,13 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SEC.PAR.001-02.xlsx
+++ b/stories/arbres/ATOM-SEC.PAR.001-02.xlsx
@@ -671,7 +671,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>jardin public</t>
+          <t>jardin public, cerceaux</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Zoé, papa</t>
+          <t>Mila, papa</t>
         </is>
       </c>
     </row>
